--- a/Spark/Data/Simulated/Bruno/model_run/results/tukey_sp_vs_system&costs.xlsx
+++ b/Spark/Data/Simulated/Bruno/model_run/results/tukey_sp_vs_system&costs.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -380,30 +380,35 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>param_Cp_multiplier</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>odds.ratio</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>df</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>z.ratio</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>p.value</t>
         </is>
@@ -416,22 +421,25 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.15666200096463</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.239480975893886</v>
-      </c>
-      <c r="D2" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+        <v>1.05312372383171</v>
+      </c>
+      <c r="D2">
+        <v>0.233835574378124</v>
+      </c>
+      <c r="E2" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F2">
-        <v>0.702930943643987</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0.955892903881042</v>
+        <v>0.233114423468406</v>
+      </c>
+      <c r="H2">
+        <v>0.999347665748523</v>
       </c>
     </row>
     <row r="3">
@@ -441,22 +449,25 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.857229155252975</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.178395669374784</v>
-      </c>
-      <c r="D3" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
+        <v>1.99268707932983</v>
+      </c>
+      <c r="D3">
+        <v>0.443890626627761</v>
+      </c>
+      <c r="E3" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F3">
-        <v>-0.740243051070334</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0.947050871202691</v>
+        <v>3.0951901520664</v>
+      </c>
+      <c r="H3">
+        <v>0.0168353919031546</v>
       </c>
     </row>
     <row r="4">
@@ -466,22 +477,25 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.251730688174521</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.0516440858846274</v>
-      </c>
-      <c r="D4" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+        <v>0.225529844879104</v>
+      </c>
+      <c r="D4">
+        <v>0.0496521562478004</v>
+      </c>
+      <c r="E4" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F4">
-        <v>-6.72363858567143</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0.000000000177237557963394</v>
+        <v>-6.76470570683136</v>
+      </c>
+      <c r="H4">
+        <v>0.000000000133589694861769</v>
       </c>
     </row>
     <row r="5">
@@ -491,22 +505,25 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.536014263778437</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.095442846873051</v>
-      </c>
-      <c r="D5" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>0.513157284208645</v>
+      </c>
+      <c r="D5">
+        <v>0.0980663488501484</v>
+      </c>
+      <c r="E5" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F5">
-        <v>-3.50215402596173</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0.00421317078538497</v>
+        <v>-3.49115297160001</v>
+      </c>
+      <c r="H5">
+        <v>0.00438447514482143</v>
       </c>
     </row>
     <row r="6">
@@ -516,22 +533,25 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.74112329663987</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.123558609740658</v>
-      </c>
-      <c r="D6" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
+        <v>1.89216806557124</v>
+      </c>
+      <c r="D6">
+        <v>0.336253208321877</v>
+      </c>
+      <c r="E6" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F6">
-        <v>-1.79697595086151</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0.375251099510647</v>
+        <v>3.58860414117873</v>
+      </c>
+      <c r="H6">
+        <v>0.00306623645635151</v>
       </c>
     </row>
     <row r="7">
@@ -541,22 +561,25 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.217635478613963</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.035478769904607</v>
-      </c>
-      <c r="D7" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
+        <v>0.214153227940332</v>
+      </c>
+      <c r="D7">
+        <v>0.0373558360540884</v>
+      </c>
+      <c r="E7" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F7">
-        <v>-9.35431762578143</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0.0000000000000489608353859694</v>
+        <v>-8.83459609594759</v>
+      </c>
+      <c r="H7">
+        <v>0.0000000000000373034936274053</v>
       </c>
     </row>
     <row r="8">
@@ -566,22 +589,25 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.4634147774643</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.0589679582848706</v>
-      </c>
-      <c r="D8" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
+        <v>0.487271602183227</v>
+      </c>
+      <c r="D8">
+        <v>0.0662382067629062</v>
+      </c>
+      <c r="E8" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F8">
-        <v>-6.04442659455717</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>0.0000000149782395375553</v>
+        <v>-5.28872908108311</v>
+      </c>
+      <c r="H8">
+        <v>0.00000122561267679178</v>
       </c>
     </row>
     <row r="9">
@@ -591,22 +617,25 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.293656237228928</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.0482671929664376</v>
-      </c>
-      <c r="D9" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
+        <v>0.113178756071903</v>
+      </c>
+      <c r="D9">
+        <v>0.0198459566500593</v>
+      </c>
+      <c r="E9" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F9">
-        <v>-7.45496711245866</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>0.000000000000931588139962969</v>
+        <v>-12.4253208799913</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -616,22 +645,25 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.625287019805404</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.0806420591137976</v>
-      </c>
-      <c r="D10" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
+        <v>0.257520254701119</v>
+      </c>
+      <c r="D10">
+        <v>0.0353084934784946</v>
+      </c>
+      <c r="E10" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F10">
-        <v>-3.64078107820715</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0.00252125285742177</v>
+        <v>-9.89469095869243</v>
+      </c>
+      <c r="H10">
+        <v>0.0000000000000454081217071689</v>
       </c>
     </row>
     <row r="11">
@@ -641,22 +673,865 @@
         </is>
       </c>
       <c r="B11">
-        <v>2.12931632478129</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.264353658446196</v>
-      </c>
-      <c r="D11" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
+        <v>2.27534091766757</v>
+      </c>
+      <c r="D11">
+        <v>0.302254002268889</v>
+      </c>
+      <c r="E11" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F11">
-        <v>6.0878268866033</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>0.0000000114342453283456</v>
+        <v>6.18891983532765</v>
+      </c>
+      <c r="H11">
+        <v>0.00000000605308625445389</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>(anemo-fish) / (ant-domatia)</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.1</v>
+      </c>
+      <c r="C12">
+        <v>1.08268086751302</v>
+      </c>
+      <c r="D12">
+        <v>0.239622742902084</v>
+      </c>
+      <c r="E12" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0.358932703306331</v>
+      </c>
+      <c r="H12">
+        <v>0.996457987319868</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>(anemo-fish) / (ant-EFN)</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.1</v>
+      </c>
+      <c r="C13">
+        <v>1.38111457126649</v>
+      </c>
+      <c r="D13">
+        <v>0.306887285727917</v>
+      </c>
+      <c r="E13" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1.45313688721923</v>
+      </c>
+      <c r="H13">
+        <v>0.593101307630399</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>(anemo-fish) / dispersal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.1</v>
+      </c>
+      <c r="C14">
+        <v>0.228504436736928</v>
+      </c>
+      <c r="D14">
+        <v>0.0501492130660687</v>
+      </c>
+      <c r="E14" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>-6.72629039178136</v>
+      </c>
+      <c r="H14">
+        <v>0.000000000174040004630172</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>(anemo-fish) / pollination</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>0.1</v>
+      </c>
+      <c r="C15">
+        <v>0.512571843340856</v>
+      </c>
+      <c r="D15">
+        <v>0.0976170691561235</v>
+      </c>
+      <c r="E15" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>-3.50921354921763</v>
+      </c>
+      <c r="H15">
+        <v>0.00410649962976828</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>(ant-domatia) / (ant-EFN)</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.1</v>
+      </c>
+      <c r="C16">
+        <v>1.27564327837341</v>
+      </c>
+      <c r="D16">
+        <v>0.226437402483842</v>
+      </c>
+      <c r="E16" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1.37148764721598</v>
+      </c>
+      <c r="H16">
+        <v>0.646028094487119</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>(ant-domatia) / dispersal</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>0.1</v>
+      </c>
+      <c r="C17">
+        <v>0.211054285333235</v>
+      </c>
+      <c r="D17">
+        <v>0.0367386178396203</v>
+      </c>
+      <c r="E17" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>-8.93676700670326</v>
+      </c>
+      <c r="H17">
+        <v>0.0000000000000345279360658424</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>(ant-domatia) / pollination</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>0.1</v>
+      </c>
+      <c r="C18">
+        <v>0.473428374621842</v>
+      </c>
+      <c r="D18">
+        <v>0.0642272625526845</v>
+      </c>
+      <c r="E18" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>-5.51180686341608</v>
+      </c>
+      <c r="H18">
+        <v>0.000000354031168603441</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>(ant-EFN) / dispersal</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>0.1</v>
+      </c>
+      <c r="C19">
+        <v>0.165449298335466</v>
+      </c>
+      <c r="D19">
+        <v>0.0289847885261631</v>
+      </c>
+      <c r="E19" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>-10.2694645576187</v>
+      </c>
+      <c r="H19">
+        <v>0.0000000000000555111512312578</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>(ant-EFN) / pollination</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>0.1</v>
+      </c>
+      <c r="C20">
+        <v>0.371129125711002</v>
+      </c>
+      <c r="D20">
+        <v>0.0508794497325798</v>
+      </c>
+      <c r="E20" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>-7.23013185172417</v>
+      </c>
+      <c r="H20">
+        <v>0.00000000000486000129029662</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dispersal / pollination</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.1</v>
+      </c>
+      <c r="C21">
+        <v>2.24315926053974</v>
+      </c>
+      <c r="D21">
+        <v>0.297471317675313</v>
+      </c>
+      <c r="E21" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>6.09206732421131</v>
+      </c>
+      <c r="H21">
+        <v>0.0000000111354607756908</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>(anemo-fish) / (ant-domatia)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.3</v>
+      </c>
+      <c r="C22">
+        <v>1.13401716461754</v>
+      </c>
+      <c r="D22">
+        <v>0.250148027191558</v>
+      </c>
+      <c r="E22" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>0.570147171003167</v>
+      </c>
+      <c r="H22">
+        <v>0.979391955128918</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>(anemo-fish) / (ant-EFN)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.3</v>
+      </c>
+      <c r="C23">
+        <v>0.764417064011289</v>
+      </c>
+      <c r="D23">
+        <v>0.169410567395362</v>
+      </c>
+      <c r="E23" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>-1.21216955921619</v>
+      </c>
+      <c r="H23">
+        <v>0.744335098515254</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>(anemo-fish) / dispersal</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>0.3</v>
+      </c>
+      <c r="C24">
+        <v>0.241256340043382</v>
+      </c>
+      <c r="D24">
+        <v>0.0527743156470095</v>
+      </c>
+      <c r="E24" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>-6.50015527323232</v>
+      </c>
+      <c r="H24">
+        <v>0.000000000802093280682925</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>(anemo-fish) / pollination</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>0.3</v>
+      </c>
+      <c r="C25">
+        <v>0.530594730827056</v>
+      </c>
+      <c r="D25">
+        <v>0.100685863230571</v>
+      </c>
+      <c r="E25" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>-3.33977373680563</v>
+      </c>
+      <c r="H25">
+        <v>0.0074858860796061</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>(ant-domatia) / (ant-EFN)</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>0.3</v>
+      </c>
+      <c r="C26">
+        <v>0.674078918610636</v>
+      </c>
+      <c r="D26">
+        <v>0.119519075153509</v>
+      </c>
+      <c r="E26" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>-2.2244330043968</v>
+      </c>
+      <c r="H26">
+        <v>0.170584960400366</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>(ant-domatia) / dispersal</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>0.3</v>
+      </c>
+      <c r="C27">
+        <v>0.212744875096092</v>
+      </c>
+      <c r="D27">
+        <v>0.0369544429621263</v>
+      </c>
+      <c r="E27" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>-8.90981022941729</v>
+      </c>
+      <c r="H27">
+        <v>0.0000000000000359712259978551</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>(ant-domatia) / pollination</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>0.3</v>
+      </c>
+      <c r="C28">
+        <v>0.467889505892979</v>
+      </c>
+      <c r="D28">
+        <v>0.0633488055331282</v>
+      </c>
+      <c r="E28" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>-5.6097804750781</v>
+      </c>
+      <c r="H28">
+        <v>0.000000202049681097272</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>(ant-EFN) / dispersal</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>0.3</v>
+      </c>
+      <c r="C29">
+        <v>0.315608260727968</v>
+      </c>
+      <c r="D29">
+        <v>0.0552363163492689</v>
+      </c>
+      <c r="E29" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>-6.58943898357584</v>
+      </c>
+      <c r="H29">
+        <v>0.000000000441387482119637</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>(ant-EFN) / pollination</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>0.3</v>
+      </c>
+      <c r="C30">
+        <v>0.694116805873947</v>
+      </c>
+      <c r="D30">
+        <v>0.0951441232542056</v>
+      </c>
+      <c r="E30" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>-2.66366924080983</v>
+      </c>
+      <c r="H30">
+        <v>0.0594784899123945</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dispersal / pollination</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>0.3</v>
+      </c>
+      <c r="C31">
+        <v>2.19929859970372</v>
+      </c>
+      <c r="D31">
+        <v>0.291133843230226</v>
+      </c>
+      <c r="E31" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>5.95379726681159</v>
+      </c>
+      <c r="H31">
+        <v>0.0000000261652060018491</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>(anemo-fish) / (ant-domatia)</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>0.5</v>
+      </c>
+      <c r="C32">
+        <v>1.09469631148058</v>
+      </c>
+      <c r="D32">
+        <v>0.241360876353065</v>
+      </c>
+      <c r="E32" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>0.410359880252512</v>
+      </c>
+      <c r="H32">
+        <v>0.994058080068953</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>(anemo-fish) / (ant-EFN)</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>0.5</v>
+      </c>
+      <c r="C33">
+        <v>0.465917853218519</v>
+      </c>
+      <c r="D33">
+        <v>0.103221129977626</v>
+      </c>
+      <c r="E33" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>-3.44738397392188</v>
+      </c>
+      <c r="H33">
+        <v>0.00513113723897052</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>(anemo-fish) / dispersal</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>0.5</v>
+      </c>
+      <c r="C34">
+        <v>0.219186266284872</v>
+      </c>
+      <c r="D34">
+        <v>0.0479222609532076</v>
+      </c>
+      <c r="E34" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>-6.94224823114399</v>
+      </c>
+      <c r="H34">
+        <v>0.0000000000386221055137526</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>(anemo-fish) / pollination</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>0.5</v>
+      </c>
+      <c r="C35">
+        <v>0.483391779613835</v>
+      </c>
+      <c r="D35">
+        <v>0.0916787495029007</v>
+      </c>
+      <c r="E35" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>-3.83285038934923</v>
+      </c>
+      <c r="H35">
+        <v>0.00119637621020452</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>(ant-domatia) / (ant-EFN)</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>0.5</v>
+      </c>
+      <c r="C36">
+        <v>0.42561379656826</v>
+      </c>
+      <c r="D36">
+        <v>0.0754610172430318</v>
+      </c>
+      <c r="E36" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>-4.81797191972176</v>
+      </c>
+      <c r="H36">
+        <v>0.000014333451007098</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>(ant-domatia) / dispersal</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>0.5</v>
+      </c>
+      <c r="C37">
+        <v>0.200225636997371</v>
+      </c>
+      <c r="D37">
+        <v>0.0347699088205277</v>
+      </c>
+      <c r="E37" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>-9.26159940934467</v>
+      </c>
+      <c r="H37">
+        <v>0.0000000000000536237720893951</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>(ant-domatia) / pollination</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>0.5</v>
+      </c>
+      <c r="C38">
+        <v>0.44157614723306</v>
+      </c>
+      <c r="D38">
+        <v>0.0597733619123198</v>
+      </c>
+      <c r="E38" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>-6.03858392300802</v>
+      </c>
+      <c r="H38">
+        <v>0.0000000155304660243161</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>(ant-EFN) / dispersal</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>0.5</v>
+      </c>
+      <c r="C39">
+        <v>0.470439724021632</v>
+      </c>
+      <c r="D39">
+        <v>0.0823267371195922</v>
+      </c>
+      <c r="E39" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>-4.3090823095035</v>
+      </c>
+      <c r="H39">
+        <v>0.000159478357680598</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>(ant-EFN) / pollination</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>0.5</v>
+      </c>
+      <c r="C40">
+        <v>1.03750430741086</v>
+      </c>
+      <c r="D40">
+        <v>0.142227300560457</v>
+      </c>
+      <c r="E40" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>0.268576869257892</v>
+      </c>
+      <c r="H40">
+        <v>0.998860067868689</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>dispersal / pollination</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>0.5</v>
+      </c>
+      <c r="C41">
+        <v>2.20539264529275</v>
+      </c>
+      <c r="D41">
+        <v>0.291852274196069</v>
+      </c>
+      <c r="E41" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>5.9765075246055</v>
+      </c>
+      <c r="H41">
+        <v>0.0000000227690751808396</v>
       </c>
     </row>
   </sheetData>
